--- a/output_test/Staff workload model.xlsx
+++ b/output_test/Staff workload model.xlsx
@@ -906,42 +906,42 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Poonam Yadav</t>
+          <t>Adrian Bors</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1706.12</v>
+        <v>1016.6</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>254.12</v>
+        <v>347.3</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1112.8</v>
+        <v>412.2</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>339.2</v>
+        <v>257.1</v>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>SOF1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; First time delivery: 5 groups shared by 3 lecturers for 11 weeks;   - Standard lecturers (3): 5.0h/week @ 2.5x each (one first session per week); Repeated sessions: 2 group(s) without first-session slots, repeated weekly at 1.5x;   - Total repeat rate: 6.0h/week (2.0h/group × 2 groups × 1.5x); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 327 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.4h total (107.9h initial + 21.4h resit), 43.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
+          <t>NLPG (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 10 projects x UG (16h) = 160.0h</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 6x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 456.0h; Grant CHEDDAR Funding Apr-Sep 26- PSU296: 5% of 1642h = 82.1h; Grant REMOTE: Resilient and Secure Multi-Access Interoperable Communication Fabric for TinyEdge: 20% of 1642h = 328.4h; Grant Orchestrated mobile Network for Blackpool intelligent transport: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 3x full-time PhD student × 80h/FTE; 1x assessor (8h each) = 248.0h</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Internationalisation and Visitors Coordinator: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
@@ -953,42 +953,42 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Christopher Crispin-Bailey</t>
+          <t>Alena Denisova</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1159.203333333333</v>
+        <v>1346.015</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>532.6533333333334</v>
+        <v>398.415</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>164.2</v>
+        <v>444.2</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>462.35</v>
+        <v>503.4</v>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>SYS2 (20cr): Standard (2.5x): 5.3h/teacher @ 2.5x = 13.3h; First time delivery: 5 groups shared by 3 lecturers for 11 weeks;   - Standard lecturers (3): 10.0h/week @ 2.5x each (one first session per week); Repeated sessions: 2 group(s) without first-session slots, repeated weekly at 1.5x;   - Total repeat rate: 6.0h/week (2.0h/group × 2 groups × 1.5x); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 277 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 109.6h total (91.4h initial + 18.2h resit), 36.5h per teacher; SYS3 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; First time delivery: 6 groups shared by 3 lecturers for 11 weeks;   - New/new-content lecturer: 10.0h/week @ 5x (one first session per week);   - Standard lecturers (2): 5.0h/week @ 2.5x each (one first session per week); Repeated sessions: 3 group(s) without first-session slots, repeated weekly at 1.5x;   - Total repeat rate: 9.0h/week (2.0h/group × 3 groups × 1.5x); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 275 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 108.9h total (90.8h initial + 18.2h resit), 36.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 19 students x 3h = 57.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>IDEV (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 10 scripts + 2 resits (assuming 20% of students resit) x 0.330h = 4.0h total (3.3h initial + 0.7h resit), 2.0h per teacher; PLEI (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 33 scripts + 6 resits (assuming 20% of students resit) x 0.330h = 12.9h total (10.9h initial + 2.0h resit), 6.4h per teacher; Project setting (fixed): 6.0h; Pastoral: 27 students x 3h = 81.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 4x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 280.0h</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>GTA Coordinator: 10% of 1642h = 164.2h; Union: 8% of 1642h = 123.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Ethics Committee Chair: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
@@ -1000,37 +1000,37 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Pourya Shamsolmoali</t>
+          <t>Alvaro Miyazawa</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>922.465</v>
+        <v>854.6166666666667</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>396.115</v>
+        <v>247.2166666666667</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>228.2</v>
+        <v>268.2</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>298.15</v>
+        <v>339.2</v>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>IMLO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; First time delivery: 4 groups shared by 3 lecturers for 11 weeks;   - Standard lecturers (3): 5.0h/week @ 2.5x each (one first session per week); Repeated sessions: 1 group(s) without first-session slots, repeated weekly at 1.5x;   - Total repeat rate: 3.0h/week (2.0h/group × 1 groups × 1.5x); Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 304 scripts + 60 resits (assuming 20% of students resit) x 0.330h = 120.1h total (100.3h initial + 19.8h resit), 40.0h per teacher; DATA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; First time delivery: 4 groups shared by 2 lecturers for 11 weeks;   - Standard lecturers (2): 5.0h/week @ 2.5x each (one first session per week); Repeated sessions: 2 group(s) without first-session slots, repeated weekly at 1.5x;   - Total repeat rate: 6.0h/week (2.0h/group × 2 groups × 1.5x); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 296 scripts + 59 resits (assuming 20% of students resit) x 0.330h = 117.2h total (97.7h initial + 19.5h resit), 58.6h per teacher; Project setting (fixed): 6.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>AURO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 104 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.9h total (34.3h initial + 6.6h resit), 13.6h per teacher; THE2 (20cr): Standard (2.5x): 6.7h/teacher @ 2.5x = 16.7h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 318 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 125.7h total (104.9h initial + 20.8h resit), 41.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>Other PLs: 5% of 1642h = 82.1h; Graduate School Board (Ordinary member): 2% of 1642h = 41.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Deputy CBoEs: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
@@ -1047,42 +1047,42 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Tommy Yuan</t>
+          <t>Andrew Pomfret</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1409.58</v>
+        <v>949.4433333333333</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>706.1800000000001</v>
+        <v>528.1433333333333</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>364.2</v>
+        <v>164.2</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>339.2</v>
+        <v>257.1</v>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>ENG1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; First time delivery: 4 groups shared by 3 lecturers for 11 weeks;   - New/new-content lecturer: 10.0h/week @ 5x (one first session per week);   - Standard lecturers (2): 5.0h/week @ 2.5x each (one first session per week); Repeated sessions: 1 group(s) without first-session slots, repeated weekly at 1.5x;   - Total repeat rate: 3.0h/week (2.0h/group × 1 groups × 1.5x); Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 315 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 124.7h total (104.0h initial + 20.8h resit), 41.6h per teacher; FOAM (20cr): Existing lecturer + new content (5x): 45h; First time delivery: 1 groups shared by 2 lecturers for 11 weeks;   - New/new-content lecturers (2): 10.0h/week @ 5x each (one first session per week); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; ARIA (20cr): Existing lecturer + new content (5x): 45h; First time delivery: 1 groups shared by 2 lecturers for 11 weeks;   - New/new-content lecturers (2): 10.0h/week @ 5x each (one first session per week); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>SYS1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 283 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.9h total (93.4h initial + 18.5h resit), 37.3h per teacher; SYS2 (20cr): Standard (2.5x): 5.3h/teacher @ 2.5x = 13.3h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 277 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 109.6h total (91.4h initial + 18.2h resit), 36.5h per teacher; Project setting (fixed): 6.0h; Pastoral: 11 students x 3h = 33.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 200.0h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Deputy CBoEs: 10% of 1642h = 164.2h; StAMP committee members: 0% of 1642h = 0.0h; CSCSE SQA Partnership Leader: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated; Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
@@ -1094,84 +1094,84 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Vasileios Vasilakis</t>
+          <t>Antonio Garcia-Dominguez</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>968.1950000000001</v>
+        <v>1098.72</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>272.795</v>
+        <v>279.12</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>356.2</v>
+        <v>644.6000000000001</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>NETS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; First time delivery: 2 groups shared by 2 lecturers for 5 weeks;   - Standard lecturers (2): 5.0h/week @ 2.5x each (one first session per week); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 103 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.6h total (34.0h initial + 6.6h resit), 20.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 26 students x 3h = 78.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>ELLA (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 13.2h per teacher; ENG2 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 7.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 12 students x 3h = 36.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h</t>
+          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h; Grant MOSAICO: 10% of 1642h = 164.2h; Grant SCHEME: 10% of 1642h = 164.2h</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>Deputy CBoEs: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated; Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Felix Ulrich-Oltean</t>
+          <t>Carlo Ottaviani</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>480.63</v>
+        <v>940.2816666666668</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>93.43000000000001</v>
+        <v>332.8816666666667</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>212.2</v>
+        <v>268.2</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>SAIL (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; First time delivery: 1 groups shared by 2 lecturers for 11 weeks;   - Standard lecturers (2): 5.0h/week @ 2.5x each (one first session per week); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 35 scripts + 7 resits (assuming 20% of students resit) x 0.330h = 13.9h total (11.6h initial + 2.3h resit), 6.9h per teacher</t>
+          <t>CTAP (20cr): Standard (2.5x): 5.7h/teacher @ 2.5x = 14.2h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 89 scripts + 17 resits (assuming 20% of students resit) x 0.330h = 35.0h total (29.4h initial + 5.6h resit), 11.7h per teacher; PRAD (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 56 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.1h total (18.5h initial + 3.6h resit), 11.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 26 students x 3h = 78.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE = 48.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x assessor (8h each) = 104.0h</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
@@ -1181,49 +1181,49 @@
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Kostas Barmpis</t>
+          <t>Christopher Crispin-Bailey</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1126.1</v>
+        <v>1159.203333333333</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>402.5</v>
+        <v>532.6533333333334</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>548.6</v>
+        <v>164.2</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>175</v>
+        <v>462.35</v>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>ENG1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; First time delivery: 4 groups shared by 3 lecturers for 11 weeks;   - New/new-content lecturer: 10.0h/week @ 5x (one first session per week);   - Standard lecturers (2): 5.0h/week @ 2.5x each (one first session per week); Repeated sessions: 1 group(s) without first-session slots, repeated weekly at 1.5x;   - Total repeat rate: 3.0h/week (2.0h/group × 1 groups × 1.5x); Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 315 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 124.7h total (104.0h initial + 20.8h resit), 41.6h per teacher; ENG2 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; First time delivery: 1 groups shared by 3 lecturers for 11 weeks;   - Standard lecturers (3): 5.0h/week @ 2.5x each (one first session per week); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 7.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 22 students x 3h = 66.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>SYS2 (20cr): Standard (2.5x): 5.3h/teacher @ 2.5x = 13.3h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 277 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 109.6h total (91.4h initial + 18.2h resit), 36.5h per teacher; SYS3 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 275 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 108.9h total (90.8h initial + 18.2h resit), 36.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 19 students x 3h = 57.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 56.0h; Grant MOSAICO: 10% of 1642h = 164.2h; Grant SCHEME: 10% of 1642h = 164.2h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>PGR Training Officer: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>GTA Coordinator: 10% of 1642h = 164.2h; Union: 8% of 1642h = 123.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
@@ -1235,37 +1235,37 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>James Walker</t>
+          <t>Claire Ingram</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1489.84</v>
+        <v>643.1849999999999</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>314.04</v>
+        <v>221.885</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1000.8</v>
+        <v>164.2</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>IMLO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; First time delivery: 4 groups shared by 3 lecturers for 11 weeks;   - Standard lecturers (3): 5.0h/week @ 2.5x each (one first session per week); Repeated sessions: 1 group(s) without first-session slots, repeated weekly at 1.5x;   - Total repeat rate: 3.0h/week (2.0h/group × 1 groups × 1.5x); Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 304 scripts + 60 resits (assuming 20% of students resit) x 0.330h = 120.1h total (100.3h initial + 19.8h resit), 40.0h per teacher; Project setting (fixed): 6.0h; Pastoral: 21 students x 3h = 63.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>HINT (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 58 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.8h total (19.1h initial + 3.6h resit), 11.4h per teacher; Project setting (fixed): 6.0h; Pastoral: 1 students x 3h = 3.0h; Projects: 10 projects x UG (16h) = 160.0h</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 344.0h; Grant Smart Data Donation Service (SDDS): 10% of 1642h = 164.2h; Grant IGGI: 20% of 1642h = 328.4h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Outreach and Extra-Curricular Activities: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
@@ -1275,39 +1275,39 @@
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Yan Jia</t>
+          <t>Claudio Guarnera</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>952.3700000000001</v>
+        <v>668.24</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>138.67</v>
+        <v>217.04</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>638.7</v>
+        <v>276.2</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>ROCS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; First time delivery: 2 groups shared by 2 lecturers for 11 weeks;   - Standard lecturers (2): 5.0h/week @ 2.5x each (one first session per week); Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 82 scripts + 16 resits (assuming 20% of students resit) x 0.330h = 32.3h total (27.1h initial + 5.3h resit), 16.2h per teacher; Pastoral: 9 students x 3h = 27.0h; Also teaches: Designing Safe AI (Safe AI 2), Foundations of Safe AI (Safe AI 1) (SAINTS - not included in workload)</t>
+          <t>IMLO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 304 scripts + 60 resits (assuming 20% of students resit) x 0.330h = 120.1h total (100.3h initial + 19.8h resit), 40.0h per teacher; Project setting (fixed): 6.0h; Pastoral: 10 students x 3h = 30.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h; Grant Encoding Empathy: Solving the Healthcare Workforce Crisis Through the Safe Deployment of an AI-Driven Voice-Based Clinical Conversational Assistant for Long Term Monitoring: 10% of 1642h = 164.2h; Grant Addressing the healthcare workforce crisis with a multilingual, accessible phone-based conversational agent for cataract surgery follow up.: 10% of 1642h = 164.2h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 112.0h</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
@@ -1329,84 +1329,84 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Alvaro Miyazawa</t>
+          <t>Colin Paterson</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>854.6166666666667</v>
+        <v>983.5599999999999</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>247.2166666666667</v>
+        <v>228.8</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>268.2</v>
+        <v>579.76</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>THE2 (20cr): Standard (2.5x): 6.7h/teacher @ 2.5x = 16.7h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 318 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 125.7h total (104.9h initial + 20.8h resit), 41.9h per teacher; AURO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; First time delivery: 1 groups shared by 3 lecturers for 11 weeks;   - New/new-content lecturer: 10.0h/week @ 5x (one first session per week);   - Standard lecturers (2): 5.0h/week @ 2.5x each (one first session per week); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 104 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.9h total (34.3h initial + 6.6h resit), 13.6h per teacher; Project setting (fixed): 6.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
+          <t>LPTC (20cr): Standard (2.5x): 10.0h/teacher @ 2.5x = 25.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 19 students x 3h = 57.0h; Projects: 7 projects x UG (16h) = 112.0h; Also teaches: Designing Safe AI (Safe AI 2) (SAINTS - not included in workload)</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 120.0h; Grant KTP with Advai (Industry): 3% of 1642h = 49.3h; Grant KTP with Advai: 5% of 1642h = 82.1h; Grant A STAR TO STEER BY: 5% of 1642h = 82.1h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>Deputy CBoEs: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Rob Alexander</t>
+          <t>Da Li</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>783.1849999999999</v>
+        <v>750</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>209.885</v>
+        <v>410.8</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>398.3</v>
+        <v>164.2</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>HINT (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; First time delivery: 1 groups shared by 2 lecturers for 2 weeks;   - Standard lecturers (2): 5.0h/week @ 2.5x each (one first session per week); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 58 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.8h total (19.1h initial + 3.6h resit), 11.4h per teacher; Project setting (fixed): 6.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>SYS3 (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 275 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 108.9h total (90.8h initial + 18.2h resit), 36.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>StAMP committee members: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
@@ -1416,44 +1416,44 @@
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Ian Gray</t>
+          <t>Dawn H Wood</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1439.61</v>
+        <v>778.8833333333333</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>95.41</v>
+        <v>439.6833333333333</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>348.2</v>
+        <v>164.2</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>996</v>
+        <v>175</v>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>EMBS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; First time delivery: 2 groups shared by 2 lecturers for 11 weeks;   - Standard lecturers (2): 5.0h/week @ 2.5x each (one first session per week); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 45 scripts + 9 resits (assuming 20% of students resit) x 0.330h = 17.8h total (14.9h initial + 3.0h resit), 8.9h per teacher</t>
+          <t>SOF1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 327 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.4h total (107.9h initial + 21.4h resit), 43.1h per teacher; SOF2 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 328 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.7h total (108.2h initial + 21.4h resit), 43.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 184.0h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>Deputy Head of Department (On-campus teaching): 50% of 1642h = 821.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
@@ -1463,91 +1463,91 @@
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Antonio Garcia-Dominguez</t>
+          <t>Detlef Plump</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1098.72</v>
+        <v>1088.76</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>279.12</v>
+        <v>325.16</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>644.6000000000001</v>
+        <v>260.2</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>175</v>
+        <v>503.4</v>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>ENG2 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; First time delivery: 1 groups shared by 3 lecturers for 11 weeks;   - Standard lecturers (3): 5.0h/week @ 2.5x each (one first session per week); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 7.9h per teacher; ELLA (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; First time delivery: 2 groups shared by 3 lecturers for 11 weeks;   - New/new-content lecturers (2): 10.0h/week @ 5x each (one first session per week);   - Standard lecturer: 5.0h/week @ 2.5x (one first session per week); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 13.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 12 students x 3h = 36.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>THE2 (20cr): Standard (2.5x): 6.7h/teacher @ 2.5x = 16.7h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 318 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 125.7h total (104.9h initial + 20.8h resit), 41.9h per teacher; THE3 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 313 scripts + 62 resits (assuming 20% of students resit) x 0.330h = 123.8h total (103.3h initial + 20.5h resit), 41.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 21 students x 3h = 63.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h; Grant MOSAICO: 10% of 1642h = 164.2h; Grant SCHEME: 10% of 1642h = 164.2h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x assessor (8h each) = 96.0h</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>EC Officer (on-campus): 15% of 1642h = 246.3h; Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated; Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Dimitris Kolovos</t>
+          <t>Dimitar Kazakov</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1373.82</v>
+        <v>1258.7</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>83.92</v>
+        <v>299.3</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1114.9</v>
+        <v>620.2</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>ENG2 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; First time delivery: 1 groups shared by 3 lecturers for 11 weeks;   - Standard lecturers (3): 5.0h/week @ 2.5x each (one first session per week); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 7.9h per teacher</t>
+          <t>NLPG (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 6x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 376.0h; Grant Socially-Acceptable and Trustworthy Human-Robot Teaming for Agile Industries (SYMPHONY Resubmission): 5% of 1642h = 82.1h; Grant MOSAICO: 5% of 1642h = 82.1h; Grant SCHEME: 20% of 1642h = 328.4h; Grant Cavecore: Doctoral Network on Continuous, Automated Validation, and Evaluation of Cognitive Robots in Open-Ended Environments: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 5x full-time PhD student × 80h/FTE; 1x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 456.0h</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Ethics Committee Member: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
@@ -1557,44 +1557,44 @@
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Jacob Rigby</t>
+          <t>Dimitris Kolovos</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>983.28</v>
+        <v>1373.82</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>397.78</v>
+        <v>83.92</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>246.3</v>
+        <v>1114.9</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>HCIN (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; First time delivery: 4 groups shared by 3 lecturers for 11 weeks;   - Standard lecturers (3): 5.0h/week @ 2.5x each (one first session per week); Repeated sessions: 1 group(s) without first-session slots, repeated weekly at 1.5x;   - Total repeat rate: 3.0h/week (2.0h/group × 1 groups × 1.5x); Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; Projects (40cr): Standard (2.5x): 40.0h/teacher @ 2.5x = 100.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 39.6h per teacher; Project setting (fixed): 6.0h; Pastoral: 8 students x 3h = 24.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>ENG2 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 7.9h per teacher</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>Grant EPSRC: Addressing environmental injustices through transdisciplinary science and technology: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 6x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 376.0h; Grant Socially-Acceptable and Trustworthy Human-Robot Teaming for Agile Industries (SYMPHONY Resubmission): 5% of 1642h = 82.1h; Grant MOSAICO: 5% of 1642h = 82.1h; Grant SCHEME: 20% of 1642h = 328.4h; Grant Cavecore: Doctoral Network on Continuous, Automated Validation, and Evaluation of Cognitive Robots in Open-Ended Environments: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Taught Project Coordinator: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
@@ -1604,91 +1604,91 @@
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Peter Nightingale</t>
+          <t>Fang Yan</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>1240.43</v>
+        <v>664.0133333333333</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>601.03</v>
+        <v>324.8133333333333</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>300.2</v>
+        <v>164.2</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>SAIL (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; First time delivery: 1 groups shared by 2 lecturers for 11 weeks;   - Standard lecturers (2): 5.0h/week @ 2.5x each (one first session per week); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 35 scripts + 7 resits (assuming 20% of students resit) x 0.330h = 13.9h total (11.6h initial + 2.3h resit), 6.9h per teacher; FOAM (20cr): Existing lecturer + new content (5x): 45h; First time delivery: 1 groups shared by 2 lecturers for 11 weeks;   - New/new-content lecturers (2): 10.0h/week @ 5x each (one first session per week); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; ARIA (20cr): Existing lecturer + new content (5x): 45h; First time delivery: 1 groups shared by 2 lecturers for 11 weeks;   - New/new-content lecturers (2): 10.0h/week @ 5x each (one first session per week); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>SOF2 (20cr): New lecturer (5x): 6.3h base @ 2.5x + content dev = 32h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 328 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.7h total (108.2h initial + 21.4h resit), 43.2h per teacher; THE3 (20cr): New lecturer (5x): 6.3h base @ 2.5x + content dev = 32h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 313 scripts + 62 resits (assuming 20% of students resit) x 0.330h = 123.8h total (103.3h initial + 20.5h resit), 41.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 2 projects x UG (16h) = 32.0h; Also teaches: Designing Safe AI (Safe AI 2), Foundations of Safe AI (Safe AI 1) (SAINTS - not included in workload)</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 136.0h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>UG PL: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated; Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Mike Freeman</t>
+          <t>Felix Ulrich-Oltean</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>970.4433333333333</v>
+        <v>480.63</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>549.1433333333333</v>
+        <v>93.43000000000001</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>164.2</v>
+        <v>212.2</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>257.1</v>
+        <v>175</v>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>SYS1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; First time delivery: 5 groups shared by 3 lecturers for 11 weeks;   - Standard lecturers (3): 5.0h/week @ 2.5x each (one first session per week); Repeated sessions: 2 group(s) without first-session slots, repeated weekly at 1.5x;   - Total repeat rate: 6.0h/week (2.0h/group × 2 groups × 1.5x); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 283 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.9h total (93.4h initial + 18.5h resit), 37.3h per teacher; SYS2 (20cr): Standard (2.5x): 5.3h/teacher @ 2.5x = 13.3h; First time delivery: 5 groups shared by 3 lecturers for 11 weeks;   - Standard lecturers (3): 10.0h/week @ 2.5x each (one first session per week); Repeated sessions: 2 group(s) without first-session slots, repeated weekly at 1.5x;   - Total repeat rate: 6.0h/week (2.0h/group × 2 groups × 1.5x); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 277 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 109.6h total (91.4h initial + 18.2h resit), 36.5h per teacher; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>SAIL (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 35 scripts + 7 resits (assuming 20% of students resit) x 0.330h = 13.9h total (11.6h initial + 2.3h resit), 6.9h per teacher</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 1x part-time PhD student × 48h/FTE = 48.0h</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
@@ -1698,44 +1698,44 @@
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Alena Denisova</t>
+          <t>Frank Soboczenski</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1346.015</v>
+        <v>2157.82</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>398.415</v>
+        <v>106.3</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>444.2</v>
+        <v>1794.42</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>503.4</v>
+        <v>257.1</v>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>IDEV (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; First time delivery: 1 groups shared by 2 lecturers for 11 weeks;   - Standard lecturers (2): 5.0h/week @ 2.5x each (one first session per week); Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 10 scripts + 2 resits (assuming 20% of students resit) x 0.330h = 4.0h total (3.3h initial + 0.7h resit), 2.0h per teacher; PLEI (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; First time delivery: 1 groups shared by 2 lecturers for 11 weeks;   - Standard lecturers (2): 5.0h/week @ 2.5x each (one first session per week); Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 33 scripts + 6 resits (assuming 20% of students resit) x 0.330h = 12.9h total (10.9h initial + 2.0h resit), 6.4h per teacher; Project setting (fixed): 6.0h; Pastoral: 27 students x 3h = 81.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>LLMA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Also teaches: Artificial Intelligence (AI) (SAINTS - not included in workload)</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 4x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 280.0h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 136.0h; Grant Large Language Models for lattice-theoretic reasoning of reactive programs: 11% of 1642h = 180.6h; Grant Alan Turing AI Fellowship: 80% of 1642h = 1313.6h</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>Ethics Committee Chair: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
@@ -1752,89 +1752,89 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Robbert Jongeling</t>
+          <t>Iain Bate</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>754.48</v>
+        <v>2435.6</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>415.28</v>
+        <v>30</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>164.2</v>
+        <v>588.6</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>175</v>
+        <v>1817</v>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>ENG1 (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; First time delivery: 4 groups shared by 3 lecturers for 11 weeks;   - New/new-content lecturer: 10.0h/week @ 5x (one first session per week);   - Standard lecturers (2): 5.0h/week @ 2.5x each (one first session per week); Repeated sessions: 1 group(s) without first-session slots, repeated weekly at 1.5x;   - Total repeat rate: 3.0h/week (2.0h/group × 1 groups × 1.5x); Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 315 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 124.7h total (104.0h initial + 20.8h resit), 41.6h per teacher; ELLA (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; First time delivery: 2 groups shared by 3 lecturers for 11 weeks;   - New/new-content lecturers (2): 10.0h/week @ 5x each (one first session per week);   - Standard lecturer: 5.0h/week @ 2.5x (one first session per week); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 13.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 2 students x 3h = 6.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
+          <t>Minimum administrative teaching load (from workload_parameters.yaml): 30h</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x assessor (8h each) = 96.0h; Grant SCHEME: 20% of 1642h = 328.4h</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Head of Department: 100% of 1642h = 1642.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Joe Cutting</t>
+          <t>Ian Gray</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>764.235</v>
+        <v>1439.61</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>361.035</v>
+        <v>95.41</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>228.2</v>
+        <v>348.2</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>175</v>
+        <v>996</v>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>IDEV (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; First time delivery: 1 groups shared by 2 lecturers for 11 weeks;   - Standard lecturers (2): 5.0h/week @ 2.5x each (one first session per week); Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 10 scripts + 2 resits (assuming 20% of students resit) x 0.330h = 4.0h total (3.3h initial + 0.7h resit), 2.0h per teacher; PRAD (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; First time delivery: 2 groups shared by 2 lecturers for 11 weeks;   - Standard lecturers (2): 5.0h/week @ 2.5x each (one first session per week); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 56 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.1h total (18.5h initial + 3.6h resit), 11.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 16 students x 3h = 48.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>EMBS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 45 scripts + 9 resits (assuming 20% of students resit) x 0.330h = 17.8h total (14.9h initial + 3.0h resit), 8.9h per teacher</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 184.0h</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>ECR rep: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Deputy Head of Department (On-campus teaching): 50% of 1642h = 821.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
@@ -1846,42 +1846,42 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Roberto Metere</t>
+          <t>Jacob Rigby</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>879.4416666666666</v>
+        <v>983.28</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>436.2416666666667</v>
+        <v>397.78</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>268.2</v>
+        <v>246.3</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>CTAP (20cr): Standard (2.5x): 5.7h/teacher @ 2.5x = 14.2h; First time delivery: 2 groups shared by 3 lecturers for 1 weeks;   - Standard lecturers (3): 7.5h/week @ 2.5x each (one first session per week); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 89 scripts + 17 resits (assuming 20% of students resit) x 0.330h = 35.0h total (29.4h initial + 5.6h resit), 11.7h per teacher; EHAC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; First time delivery: 2 groups shared by 2 lecturers for 11 weeks;   - Standard lecturers (2): 5.0h/week @ 2.5x each (one first session per week); Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 56 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.1h total (18.5h initial + 3.6h resit), 11.1h per teacher; CBDA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; First time delivery: 3 groups shared by 2 lecturers for 11 weeks;   - Standard lecturers (2): 5.0h/week @ 2.5x each (one first session per week); Repeated sessions: 1 group(s) without first-session slots, repeated weekly at 1.5x;   - Total repeat rate: 3.0h/week (2.0h/group × 1 groups × 1.5x); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 29 scripts + 5 resits (assuming 20% of students resit) x 0.330h = 11.2h total (9.6h initial + 1.7h resit), 5.6h per teacher; Project setting (fixed): 6.0h; Pastoral: 20 students x 3h = 60.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>HCIN (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; Projects (40cr): Standard (2.5x): 40.0h/teacher @ 2.5x = 100.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 39.6h per teacher; Project setting (fixed): 6.0h; Pastoral: 8 students x 3h = 24.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h</t>
+          <t>Grant EPSRC: Addressing environmental injustices through transdisciplinary science and technology: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>StAMP committee members: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Taught Project Coordinator: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
@@ -1893,42 +1893,42 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Jo Iacovides</t>
+          <t>James Stovold</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1037.755</v>
+        <v>1011.84</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>350.355</v>
+        <v>590.54</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>348.2</v>
+        <v>164.2</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>339.2</v>
+        <v>257.1</v>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>QUAL (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; First time delivery: 1 groups shared by 2 lecturers for 11 weeks;   - Standard lecturers (2): 5.0h/week @ 2.5x each (one first session per week); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 40 scripts + 8 resits (assuming 20% of students resit) x 0.330h = 15.8h total (13.2h initial + 2.6h resit), 7.9h per teacher; PLEI (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; First time delivery: 1 groups shared by 2 lecturers for 11 weeks;   - Standard lecturers (2): 5.0h/week @ 2.5x each (one first session per week); Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 33 scripts + 6 resits (assuming 20% of students resit) x 0.330h = 12.9h total (10.9h initial + 2.0h resit), 6.4h per teacher; Project setting (fixed): 6.0h; Pastoral: 12 students x 3h = 36.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>DEEP (20cr): New lecturer (5x): 9.0h base @ 2.5x + content dev = 45h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 130 scripts + 26 resits (assuming 20% of students resit) x 0.330h = 51.5h total (42.9h initial + 8.6h resit), 25.7h per teacher; LLMA (20cr): New lecturer (5x): 9.0h base @ 2.5x + content dev = 45h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 184.0h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>Module had 0 students - marking not calculated; Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
@@ -1940,32 +1940,32 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Sam Braunstein</t>
+          <t>James Walker</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>656.5916666666667</v>
+        <v>1489.84</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>317.3916666666667</v>
+        <v>314.04</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>164.2</v>
+        <v>1000.8</v>
       </c>
       <c r="F24" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>THE2 (20cr): Standard (2.5x): 6.7h/teacher @ 2.5x = 16.7h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 318 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 125.7h total (104.9h initial + 20.8h resit), 41.9h per teacher; QUCO (20cr): Standard (2.5x): 8.5h/teacher @ 2.5x = 21.2h; First time delivery: 1 groups shared by 2 lecturers for 11 weeks;   - Standard lecturers (2): 7.5h/week @ 2.5x each (one first session per week); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 51 scripts + 10 resits (assuming 20% of students resit) x 0.330h = 20.1h total (16.8h initial + 3.3h resit), 10.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 4 students x 3h = 12.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>IMLO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 304 scripts + 60 resits (assuming 20% of students resit) x 0.330h = 120.1h total (100.3h initial + 19.8h resit), 40.0h per teacher; Project setting (fixed): 6.0h; Pastoral: 21 students x 3h = 63.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 344.0h; Grant Smart Data Donation Service (SDDS): 10% of 1642h = 164.2h; Grant IGGI: 20% of 1642h = 328.4h</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
@@ -1987,42 +1987,42 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Steven Xiaotian Dai</t>
+          <t>Jen Beeston</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1179.32</v>
+        <v>877</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>325.62</v>
+        <v>369.8</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>350.3</v>
+        <v>332.2</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>503.4</v>
+        <v>175</v>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>HIPC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; First time delivery: 3 groups shared by 2 lecturers for 11 weeks;   - Standard lecturers (2): 5.0h/week @ 2.5x each (one first session per week); Repeated sessions: 1 group(s) without first-session slots, repeated weekly at 1.5x;   - Total repeat rate: 3.0h/week (2.0h/group × 1 groups × 1.5x); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 62 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 24.4h total (20.5h initial + 4.0h resit), 12.2h per teacher; EMBS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; First time delivery: 2 groups shared by 2 lecturers for 11 weeks;   - Standard lecturers (2): 5.0h/week @ 2.5x each (one first session per week); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 45 scripts + 9 resits (assuming 20% of students resit) x 0.330h = 17.8h total (14.9h initial + 3.0h resit), 8.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 15 students x 3h = 45.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>QUAL (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 40 scripts + 8 resits (assuming 20% of students resit) x 0.330h = 15.8h total (13.2h initial + 2.6h resit), 7.9h per teacher; TECC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 11.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 9 students x 3h = 27.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h; Grant SCHEME: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 168.0h</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>Student Disability Representative: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Chair of the Department Education Committee: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated; Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
@@ -2034,42 +2034,42 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Stefano Pirandola</t>
+          <t>Jo Iacovides</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>1257.515</v>
+        <v>1037.755</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>315.815</v>
+        <v>350.355</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>520.4000000000001</v>
+        <v>348.2</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>421.3</v>
+        <v>339.2</v>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>QUCO (20cr): Standard (2.5x): 8.5h/teacher @ 2.5x = 21.2h; First time delivery: 1 groups shared by 2 lecturers for 11 weeks;   - Standard lecturers (2): 7.5h/week @ 2.5x each (one first session per week); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 51 scripts + 10 resits (assuming 20% of students resit) x 0.330h = 20.1h total (16.8h initial + 3.3h resit), 10.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>PLEI (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 33 scripts + 6 resits (assuming 20% of students resit) x 0.330h = 12.9h total (10.9h initial + 2.0h resit), 6.4h per teacher; QUAL (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 40 scripts + 8 resits (assuming 20% of students resit) x 0.330h = 15.8h total (13.2h initial + 2.6h resit), 7.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 12 students x 3h = 36.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h; Grant Integrated Quantum Networks (IQN) Hub: 10% of 1642h = 164.2h</t>
+          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 184.0h</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Progression Panel Chair: 15% of 1642h = 246.3h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
@@ -2081,37 +2081,37 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>William Smith</t>
+          <t>Joe Cutting</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1321.76</v>
+        <v>764.235</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>347.41</v>
+        <v>361.035</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>676.2</v>
+        <v>228.2</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>298.15</v>
+        <v>175</v>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>ROCS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; First time delivery: 2 groups shared by 2 lecturers for 11 weeks;   - Standard lecturers (2): 5.0h/week @ 2.5x each (one first session per week); Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 82 scripts + 16 resits (assuming 20% of students resit) x 0.330h = 32.3h total (27.1h initial + 5.3h resit), 16.2h per teacher; DEEP (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; First time delivery: 3 groups shared by 2 lecturers for 11 weeks;   - New/new-content lecturer: 10.0h/week @ 5x (one first session per week);   - Standard lecturer: 5.0h/week @ 2.5x (one first session per week); Repeated sessions: 1 group(s) without first-session slots, repeated weekly at 1.5x;   - Total repeat rate: 3.0h/week (2.0h/group × 1 groups × 1.5x); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 130 scripts + 26 resits (assuming 20% of students resit) x 0.330h = 51.5h total (42.9h initial + 8.6h resit), 25.7h per teacher; Project setting (fixed): 6.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>IDEV (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 10 scripts + 2 resits (assuming 20% of students resit) x 0.330h = 4.0h total (3.3h initial + 0.7h resit), 2.0h per teacher; PRAD (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 56 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.1h total (18.5h initial + 3.6h resit), 11.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 16 students x 3h = 48.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 4x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 6x assessor (8h each) = 512.0h</t>
+          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Director of Admissions: 5% of 1642h = 82.1h; Internally Distributed Funding panel reviewer: 2% of 1642h = 41.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>ECR rep: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
@@ -2128,37 +2128,37 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Dimitar Kazakov</t>
+          <t>Katrina Attwood</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1094.5</v>
+        <v>1160.16</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>299.3</v>
+        <v>444.56</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>620.2</v>
+        <v>212.2</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>175</v>
+        <v>503.4</v>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>NLPG (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; First time delivery: 2 groups shared by 2 lecturers for 11 weeks;   - Standard lecturers (2): 5.0h/week @ 2.5x each (one first session per week); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>HCIN (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; TECC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 11.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 22 students x 3h = 66.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 5x full-time PhD student × 80h/FTE; 1x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 456.0h</t>
+          <t>PhD supervision: 1x part-time PhD student × 48h/FTE = 48.0h</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Ethics Committee members: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Director of Students: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>SOF1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; First time delivery: 5 groups shared by 3 lecturers for 11 weeks;   - Standard lecturers (3): 5.0h/week @ 2.5x each (one first session per week); Repeated sessions: 2 group(s) without first-session slots, repeated weekly at 1.5x;   - Total repeat rate: 6.0h/week (2.0h/group × 2 groups × 1.5x); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 327 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.4h total (107.9h initial + 21.4h resit), 43.1h per teacher; SOF2 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; First time delivery: 5 groups shared by 3 lecturers for 11 weeks;   - New/new-content lecturer: 5.0h/week @ 5x (one first session per week);   - Standard lecturers (2): 2.5h/week @ 2.5x each (one first session per week); Repeated sessions: 2 group(s) without first-session slots, repeated weekly at 1.5x;   - Total repeat rate: 3.0h/week (1.0h/group × 2 groups × 1.5x); Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 328 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.7h total (108.2h initial + 21.4h resit), 43.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>SOF1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 327 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.4h total (107.9h initial + 21.4h resit), 43.1h per teacher; SOF2 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 328 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.7h total (108.2h initial + 21.4h resit), 43.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -2222,84 +2222,84 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Dawn H Wood</t>
+          <t>Kostas Barmpis</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>778.8833333333333</v>
+        <v>1126.1</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>439.6833333333333</v>
+        <v>402.5</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>164.2</v>
+        <v>548.6</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>SOF1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; First time delivery: 5 groups shared by 3 lecturers for 11 weeks;   - Standard lecturers (3): 5.0h/week @ 2.5x each (one first session per week); Repeated sessions: 2 group(s) without first-session slots, repeated weekly at 1.5x;   - Total repeat rate: 6.0h/week (2.0h/group × 2 groups × 1.5x); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 327 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.4h total (107.9h initial + 21.4h resit), 43.1h per teacher; SOF2 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; First time delivery: 5 groups shared by 3 lecturers for 11 weeks;   - New/new-content lecturer: 5.0h/week @ 5x (one first session per week);   - Standard lecturers (2): 2.5h/week @ 2.5x each (one first session per week); Repeated sessions: 2 group(s) without first-session slots, repeated weekly at 1.5x;   - Total repeat rate: 3.0h/week (1.0h/group × 2 groups × 1.5x); Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 328 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.7h total (108.2h initial + 21.4h resit), 43.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>ENG1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 315 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 124.7h total (104.0h initial + 20.8h resit), 41.6h per teacher; ENG2 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 7.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 22 students x 3h = 66.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 56.0h; Grant MOSAICO: 10% of 1642h = 164.2h; Grant SCHEME: 10% of 1642h = 164.2h</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>PGR Training Officer: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Pengcheng Liu</t>
+          <t>Mike Freeman</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1400.88</v>
+        <v>970.4433333333333</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>229.3</v>
+        <v>549.1433333333333</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>996.5800000000002</v>
+        <v>164.2</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>SYS3 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; First time delivery: 6 groups shared by 3 lecturers for 11 weeks;   - New/new-content lecturer: 10.0h/week @ 5x (one first session per week);   - Standard lecturers (2): 5.0h/week @ 2.5x each (one first session per week); Repeated sessions: 3 group(s) without first-session slots, repeated weekly at 1.5x;   - Total repeat rate: 9.0h/week (2.0h/group × 3 groups × 1.5x); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 275 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 108.9h total (90.8h initial + 18.2h resit), 36.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 10 students x 3h = 30.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
+          <t>SYS1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 283 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.9h total (93.4h initial + 18.5h resit), 37.3h per teacher; SYS2 (20cr): Standard (2.5x): 5.3h/teacher @ 2.5x = 13.3h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 277 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 109.6h total (91.4h initial + 18.2h resit), 36.5h per teacher; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h; Grant Intelligent Dependable Environment Control for Sustainable Aquaculture: 20% of 1642h = 328.4h; Grant Establishing a Safe AI Research Hub: York–UTM–UTB Twin-Lab Initiative: 9% of 1642h = 147.8h; Grant Establishment of Korea–UK Collaboration Platform for Convergent Research in Quantum Photonics and Artificial Intelligence - Yr2: 5% of 1642h = 82.1h; Grant SCHEME: 5% of 1642h = 82.1h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Graduate School Board (GSB) Chair: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
@@ -2316,37 +2316,37 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Radu Calinescu</t>
+          <t>Mike O'Dea</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>1244.13</v>
+        <v>619.875</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>150.43</v>
+        <v>198.575</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>918.7</v>
+        <v>164.2</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>GPIG (40cr): Standard (2.5x): 19.0h/teacher @ 2.5x = 47.5h; First time delivery: 1 groups shared by 2 lecturers for 4 weeks;   - Standard lecturers (2): 5.0h/week @ 2.5x each (one first session per week); Assessment setting: 6 paper(s) set (3 assessment(s), manual): 15.0h each (11.2h main + 11.2h resit); 35 scripts + 7 resits (assuming 20% of students resit) x 0.330h = 13.9h total (11.6h initial + 2.3h resit), 6.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 9 students x 3h = 27.0h; Projects: 1 projects x UG (16h) = 16.0h</t>
+          <t>CBDA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 29 scripts + 5 resits (assuming 20% of students resit) x 0.330h = 11.2h total (9.6h initial + 1.7h resit), 5.6h per teacher; GODS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 18 scripts + 3 resits (assuming 20% of students resit) x 0.330h = 6.9h total (5.9h initial + 1.0h resit), 3.5h per teacher</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 5x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 344.0h; Grant ARISE: Accelerating ReIntroduction of EcoSystem-Engineering Ant Colonies with Embodied AI: 10% of 1642h = 164.2h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h; Grant MammoBot: Robotic Posture Assistance for Universal Breast Screening Access: 10% of 1642h = 164.2h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
@@ -2356,44 +2356,44 @@
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Claire Ingram</t>
+          <t>Nick Pears</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>643.1849999999999</v>
+        <v>1473.013333333333</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>221.885</v>
+        <v>213.0133333333333</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>164.2</v>
+        <v>428.2</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>257.1</v>
+        <v>831.8000000000001</v>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>HINT (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; First time delivery: 1 groups shared by 2 lecturers for 2 weeks;   - Standard lecturers (2): 5.0h/week @ 2.5x each (one first session per week); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 58 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.8h total (19.1h initial + 3.6h resit), 11.4h per teacher; Project setting (fixed): 6.0h; Pastoral: 1 students x 3h = 3.0h; Projects: 10 projects x UG (16h) = 160.0h</t>
+          <t>THE1 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 264.0h</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Outreach and Extra-Curricular Activities: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Deputy Head (Research): 40% of 1642h = 656.8h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
@@ -2410,37 +2410,37 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Da Li</t>
+          <t>Paul Cairns</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>750</v>
+        <v>1608.945</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>410.8</v>
+        <v>257.145</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>164.2</v>
+        <v>1012.6</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>SYS3 (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; First time delivery: 6 groups shared by 3 lecturers for 11 weeks;   - New/new-content lecturer: 10.0h/week @ 5x (one first session per week);   - Standard lecturers (2): 5.0h/week @ 2.5x each (one first session per week); Repeated sessions: 3 group(s) without first-session slots, repeated weekly at 1.5x;   - Total repeat rate: 9.0h/week (2.0h/group × 3 groups × 1.5x); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 275 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 108.9h total (90.8h initial + 18.2h resit), 36.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>GODS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 18 scripts + 3 resits (assuming 20% of students resit) x 0.330h = 6.9h total (5.9h initial + 1.0h resit), 3.5h per teacher; HCIN (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 1 projects x UG (16h) = 16.0h</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 4x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 7x assessor (8h each) = 520.0h; Grant BiB Centre for Social Change: 0% of 1642h = 0.0h; Grant IGGI: 20% of 1642h = 328.4h</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Other PLs: 5% of 1642h = 82.1h; REF Lead: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
@@ -2450,44 +2450,44 @@
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Siamak Shahandashti</t>
+          <t>Pedro Ribeiro</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>1117.84</v>
+        <v>1329.73</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>300.34</v>
+        <v>345.93</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>478.3</v>
+        <v>644.6</v>
       </c>
       <c r="F35" s="3" t="n">
         <v>339.2</v>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>THE1 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; First time delivery: 4 groups shared by 3 lecturers for 11 weeks;   - Standard lecturers (3): 2.5h/week @ 2.5x each (one first session per week); Repeated sessions: 1 group(s) without first-session slots, repeated weekly at 1.5x;   - Total repeat rate: 1.5h/week (1.0h/group × 1 groups × 1.5x); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; CTAP (20cr): Standard (2.5x): 5.7h/teacher @ 2.5x = 14.2h; First time delivery: 2 groups shared by 3 lecturers for 1 weeks;   - Standard lecturers (3): 7.5h/week @ 2.5x each (one first session per week); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 89 scripts + 17 resits (assuming 20% of students resit) x 0.330h = 35.0h total (29.4h initial + 5.6h resit), 11.7h per teacher; Project setting (fixed): 6.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>AURO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 104 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.9h total (34.3h initial + 6.6h resit), 13.6h per teacher; SYS1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 283 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.9h total (93.4h initial + 18.5h resit), 37.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 232.0h; Grant Participatory Harm Auditing Workbenches &amp; Methodologies: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h; Grant Large Language Models for lattice-theoretic reasoning of reactive programs: 20% of 1642h = 328.4h</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Deputy Graduate Chair: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
@@ -2504,37 +2504,37 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Fang Yan</t>
+          <t>Pengcheng Liu</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>664.0133333333333</v>
+        <v>1400.88</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>324.8133333333333</v>
+        <v>229.3</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>164.2</v>
+        <v>996.5800000000002</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>SOF2 (20cr): New lecturer (5x): 6.3h base @ 2.5x + content dev = 32h; First time delivery: 5 groups shared by 3 lecturers for 11 weeks;   - New/new-content lecturer: 5.0h/week @ 5x (one first session per week);   - Standard lecturers (2): 2.5h/week @ 2.5x each (one first session per week); Repeated sessions: 2 group(s) without first-session slots, repeated weekly at 1.5x;   - Total repeat rate: 3.0h/week (1.0h/group × 2 groups × 1.5x); Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 328 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.7h total (108.2h initial + 21.4h resit), 43.2h per teacher; THE3 (20cr): New lecturer (5x): 6.3h base @ 2.5x + content dev = 32h; First time delivery: 5 groups shared by 3 lecturers for 3 weeks;   - New/new-content lecturer: 5.0h/week @ 5x (one first session per week);   - Standard lecturers (2): 2.5h/week @ 2.5x each (one first session per week); Repeated sessions: 2 group(s) without first-session slots, repeated weekly at 1.5x;   - Total repeat rate: 3.0h/week (1.0h/group × 2 groups × 1.5x); Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 313 scripts + 62 resits (assuming 20% of students resit) x 0.330h = 123.8h total (103.3h initial + 20.5h resit), 41.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 2 projects x UG (16h) = 32.0h; Also teaches: Designing Safe AI (Safe AI 2), Foundations of Safe AI (Safe AI 1) (SAINTS - not included in workload)</t>
+          <t>SYS3 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 275 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 108.9h total (90.8h initial + 18.2h resit), 36.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 10 students x 3h = 30.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h; Grant Intelligent Dependable Environment Control for Sustainable Aquaculture: 20% of 1642h = 328.4h; Grant Establishing a Safe AI Research Hub: York–UTM–UTB Twin-Lab Initiative: 9% of 1642h = 147.8h; Grant Establishment of Korea–UK Collaboration Platform for Convergent Research in Quantum Photonics and Artificial Intelligence - Yr2: 5% of 1642h = 82.1h; Grant SCHEME: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Graduate School Board (GSB) Chair: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
@@ -2544,49 +2544,49 @@
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Mike O'Dea</t>
+          <t>Peter Nightingale</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>619.875</v>
+        <v>1240.43</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>198.575</v>
+        <v>601.03</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>164.2</v>
+        <v>300.2</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>257.1</v>
+        <v>339.2</v>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>CBDA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; First time delivery: 3 groups shared by 2 lecturers for 11 weeks;   - Standard lecturers (2): 5.0h/week @ 2.5x each (one first session per week); Repeated sessions: 1 group(s) without first-session slots, repeated weekly at 1.5x;   - Total repeat rate: 3.0h/week (2.0h/group × 1 groups × 1.5x); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 29 scripts + 5 resits (assuming 20% of students resit) x 0.330h = 11.2h total (9.6h initial + 1.7h resit), 5.6h per teacher; GODS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; First time delivery: 2 groups shared by 2 lecturers for 11 weeks;   - Standard lecturers (2): 5.0h/week @ 2.5x each (one first session per week); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 18 scripts + 3 resits (assuming 20% of students resit) x 0.330h = 6.9h total (5.9h initial + 1.0h resit), 3.5h per teacher</t>
+          <t>ARIA (20cr): Existing lecturer + new content (5x): 45h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; FOAM (20cr): Existing lecturer + new content (5x): 45h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; SAIL (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 35 scripts + 7 resits (assuming 20% of students resit) x 0.330h = 13.9h total (11.6h initial + 2.3h resit), 6.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 136.0h</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>UG PL: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated; Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
@@ -2598,84 +2598,84 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Colin Paterson</t>
+          <t>Poonam Yadav</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>983.5599999999999</v>
+        <v>1706.12</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>228.8</v>
+        <v>254.12</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>579.76</v>
+        <v>1112.8</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>LPTC (20cr): Standard (2.5x): 10.0h/teacher @ 2.5x = 25.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 19 students x 3h = 57.0h; Projects: 7 projects x UG (16h) = 112.0h; Also teaches: Designing Safe AI (Safe AI 2) (SAINTS - not included in workload)</t>
+          <t>SOF1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 327 scripts + 65 resits (assuming 20% of students resit) x 0.330h = 129.4h total (107.9h initial + 21.4h resit), 43.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 120.0h; Grant KTP with Advai (Industry): 3% of 1642h = 49.3h; Grant KTP with Advai: 5% of 1642h = 82.1h; Grant A STAR TO STEER BY: 5% of 1642h = 82.1h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 6x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 456.0h; Grant CHEDDAR Funding Apr-Sep 26- PSU296: 5% of 1642h = 82.1h; Grant REMOTE: Resilient and Secure Multi-Access Interoperable Communication Fabric for TinyEdge: 20% of 1642h = 328.4h; Grant Orchestrated mobile Network for Blackpool intelligent transport: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Xinwei Fang</t>
+          <t>Pourya Shamsolmoali</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>925.8049999999999</v>
+        <v>922.465</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>424.505</v>
+        <v>396.115</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>244.2</v>
+        <v>228.2</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>257.1</v>
+        <v>298.15</v>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>DATA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; First time delivery: 4 groups shared by 2 lecturers for 11 weeks;   - Standard lecturers (2): 5.0h/week @ 2.5x each (one first session per week); Repeated sessions: 2 group(s) without first-session slots, repeated weekly at 1.5x;   - Total repeat rate: 6.0h/week (2.0h/group × 2 groups × 1.5x); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 296 scripts + 59 resits (assuming 20% of students resit) x 0.330h = 117.2h total (97.7h initial + 19.5h resit), 58.6h per teacher; GPIG (40cr): Standard (2.5x): 19.0h/teacher @ 2.5x = 47.5h; First time delivery: 1 groups shared by 2 lecturers for 4 weeks;   - Standard lecturers (2): 5.0h/week @ 2.5x each (one first session per week); Assessment setting: 6 paper(s) set (3 assessment(s), manual): 15.0h each (11.2h main + 11.2h resit); 35 scripts + 7 resits (assuming 20% of students resit) x 0.330h = 13.9h total (11.6h initial + 2.3h resit), 6.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 9 students x 3h = 27.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>DATA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 296 scripts + 59 resits (assuming 20% of students resit) x 0.330h = 117.2h total (97.7h initial + 19.5h resit), 58.6h per teacher; IMLO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 304 scripts + 60 resits (assuming 20% of students resit) x 0.330h = 120.1h total (100.3h initial + 19.8h resit), 40.0h per teacher; Project setting (fixed): 6.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE = 80.0h</t>
+          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Graduate School Board (Ordinary member): 2% of 1642h = 41.1h; Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
@@ -2692,37 +2692,37 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Pedro Ribeiro</t>
+          <t>Radu Calinescu</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1329.73</v>
+        <v>1244.13</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>345.93</v>
+        <v>150.43</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>644.6</v>
+        <v>918.7</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>SYS1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; First time delivery: 5 groups shared by 3 lecturers for 11 weeks;   - Standard lecturers (3): 5.0h/week @ 2.5x each (one first session per week); Repeated sessions: 2 group(s) without first-session slots, repeated weekly at 1.5x;   - Total repeat rate: 6.0h/week (2.0h/group × 2 groups × 1.5x); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 283 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.9h total (93.4h initial + 18.5h resit), 37.3h per teacher; AURO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; First time delivery: 1 groups shared by 3 lecturers for 11 weeks;   - New/new-content lecturer: 10.0h/week @ 5x (one first session per week);   - Standard lecturers (2): 5.0h/week @ 2.5x each (one first session per week); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 104 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.9h total (34.3h initial + 6.6h resit), 13.6h per teacher; Project setting (fixed): 6.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>GPIG (40cr): Standard (2.5x): 19.0h/teacher @ 2.5x = 47.5h; Assessment setting: 6 paper(s) set (3 assessment(s), manual): 15.0h each (11.2h main + 11.2h resit); 35 scripts + 7 resits (assuming 20% of students resit) x 0.330h = 13.9h total (11.6h initial + 2.3h resit), 6.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 9 students x 3h = 27.0h; Projects: 1 projects x UG (16h) = 16.0h</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h; Grant Large Language Models for lattice-theoretic reasoning of reactive programs: 20% of 1642h = 328.4h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 5x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 344.0h; Grant ARISE: Accelerating ReIntroduction of EcoSystem-Engineering Ant Colonies with Embodied AI: 10% of 1642h = 164.2h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h; Grant MammoBot: Robotic Posture Assistance for Universal Breast Screening Access: 10% of 1642h = 164.2h</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
@@ -2732,49 +2732,49 @@
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Katrina Attwood</t>
+          <t>Rob Alexander</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>1160.16</v>
+        <v>783.1849999999999</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>444.56</v>
+        <v>209.885</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>212.2</v>
+        <v>398.3</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>503.4</v>
+        <v>175</v>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>HCIN (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; First time delivery: 4 groups shared by 3 lecturers for 11 weeks;   - Standard lecturers (3): 5.0h/week @ 2.5x each (one first session per week); Repeated sessions: 1 group(s) without first-session slots, repeated weekly at 1.5x;   - Total repeat rate: 3.0h/week (2.0h/group × 1 groups × 1.5x); Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; TECC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; First time delivery: 2 groups shared by 2 lecturers for 11 weeks;   - Standard lecturers (2): 5.0h/week @ 2.5x each (one first session per week); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 11.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 22 students x 3h = 66.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>HINT (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 58 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.8h total (19.1h initial + 3.6h resit), 11.4h per teacher; Project setting (fixed): 6.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE = 48.0h</t>
+          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>Director of Students: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>StAMP committee members: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
@@ -2786,17 +2786,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Soumya Banerjee</t>
+          <t>Robbert Jongeling</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>856.04</v>
+        <v>754.48</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>516.8399999999999</v>
+        <v>415.28</v>
       </c>
       <c r="E42" s="3" t="n">
         <v>164.2</v>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>AURO (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; First time delivery: 1 groups shared by 3 lecturers for 11 weeks;   - New/new-content lecturer: 10.0h/week @ 5x (one first session per week);   - Standard lecturers (2): 5.0h/week @ 2.5x each (one first session per week); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 104 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.9h total (34.3h initial + 6.6h resit), 13.6h per teacher; ELLA (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; First time delivery: 2 groups shared by 3 lecturers for 11 weeks;   - New/new-content lecturers (2): 10.0h/week @ 5x each (one first session per week);   - Standard lecturer: 5.0h/week @ 2.5x (one first session per week); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 13.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>ELLA (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 13.2h per teacher; ENG1 (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 315 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 124.7h total (104.0h initial + 20.8h resit), 41.6h per teacher; Project setting (fixed): 6.0h; Pastoral: 2 students x 3h = 6.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -2833,37 +2833,37 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Nick Pears</t>
+          <t>Roberto Metere</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1473.013333333333</v>
+        <v>879.4416666666666</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>213.0133333333333</v>
+        <v>436.2416666666667</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>428.2</v>
+        <v>268.2</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>831.8000000000001</v>
+        <v>175</v>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>THE1 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; First time delivery: 4 groups shared by 3 lecturers for 11 weeks;   - Standard lecturers (3): 2.5h/week @ 2.5x each (one first session per week); Repeated sessions: 1 group(s) without first-session slots, repeated weekly at 1.5x;   - Total repeat rate: 1.5h/week (1.0h/group × 1 groups × 1.5x); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>CBDA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 29 scripts + 5 resits (assuming 20% of students resit) x 0.330h = 11.2h total (9.6h initial + 1.7h resit), 5.6h per teacher; CTAP (20cr): Standard (2.5x): 5.7h/teacher @ 2.5x = 14.2h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 89 scripts + 17 resits (assuming 20% of students resit) x 0.330h = 35.0h total (29.4h initial + 5.6h resit), 11.7h per teacher; EHAC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 56 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.1h total (18.5h initial + 3.6h resit), 11.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 20 students x 3h = 60.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 264.0h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>Deputy Head (Research): 40% of 1642h = 656.8h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>StAMP committee members: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
@@ -2880,84 +2880,84 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Jen Beeston</t>
+          <t>Sam Braunstein</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>877</v>
+        <v>656.5916666666667</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>369.8</v>
+        <v>317.3916666666667</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>332.2</v>
+        <v>164.2</v>
       </c>
       <c r="F44" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>QUAL (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; First time delivery: 1 groups shared by 2 lecturers for 11 weeks;   - Standard lecturers (2): 5.0h/week @ 2.5x each (one first session per week); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 40 scripts + 8 resits (assuming 20% of students resit) x 0.330h = 15.8h total (13.2h initial + 2.6h resit), 7.9h per teacher; TECC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; First time delivery: 2 groups shared by 2 lecturers for 11 weeks;   - Standard lecturers (2): 5.0h/week @ 2.5x each (one first session per week); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 60 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 23.8h total (19.8h initial + 4.0h resit), 11.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 9 students x 3h = 27.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>QUCO (20cr): Standard (2.5x): 8.5h/teacher @ 2.5x = 21.2h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 51 scripts + 10 resits (assuming 20% of students resit) x 0.330h = 20.1h total (16.8h initial + 3.3h resit), 10.1h per teacher; THE2 (20cr): Standard (2.5x): 6.7h/teacher @ 2.5x = 16.7h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 318 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 125.7h total (104.9h initial + 20.8h resit), 41.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 4 students x 3h = 12.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 168.0h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>Chair of the Department Education Committee: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated; Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Andrew Pomfret</t>
+          <t>Siamak Shahandashti</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>949.4433333333333</v>
+        <v>1117.84</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>528.1433333333333</v>
+        <v>300.34</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>164.2</v>
+        <v>478.3</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>257.1</v>
+        <v>339.2</v>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>SYS1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; First time delivery: 5 groups shared by 3 lecturers for 11 weeks;   - Standard lecturers (3): 5.0h/week @ 2.5x each (one first session per week); Repeated sessions: 2 group(s) without first-session slots, repeated weekly at 1.5x;   - Total repeat rate: 6.0h/week (2.0h/group × 2 groups × 1.5x); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 283 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.9h total (93.4h initial + 18.5h resit), 37.3h per teacher; SYS2 (20cr): Standard (2.5x): 5.3h/teacher @ 2.5x = 13.3h; First time delivery: 5 groups shared by 3 lecturers for 11 weeks;   - Standard lecturers (3): 10.0h/week @ 2.5x each (one first session per week); Repeated sessions: 2 group(s) without first-session slots, repeated weekly at 1.5x;   - Total repeat rate: 6.0h/week (2.0h/group × 2 groups × 1.5x); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 277 scripts + 55 resits (assuming 20% of students resit) x 0.330h = 109.6h total (91.4h initial + 18.2h resit), 36.5h per teacher; Project setting (fixed): 6.0h; Pastoral: 11 students x 3h = 33.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>CTAP (20cr): Standard (2.5x): 5.7h/teacher @ 2.5x = 14.2h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 89 scripts + 17 resits (assuming 20% of students resit) x 0.330h = 35.0h total (29.4h initial + 5.6h resit), 11.7h per teacher; THE1 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 232.0h; Grant Participatory Harm Auditing Workbenches &amp; Methodologies: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Deputy Graduate Chair: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
@@ -2974,131 +2974,131 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Adrian Bors</t>
+          <t>Simon Foster</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>1016.6</v>
+        <v>728.2966666666666</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>347.3</v>
+        <v>277.0966666666666</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>412.2</v>
+        <v>276.2</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>257.1</v>
+        <v>175</v>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>NLPG (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; First time delivery: 2 groups shared by 2 lecturers for 11 weeks;   - Standard lecturers (2): 5.0h/week @ 2.5x each (one first session per week); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 10 projects x UG (16h) = 160.0h</t>
+          <t>THE1 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; THE3 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 313 scripts + 62 resits (assuming 20% of students resit) x 0.330h = 123.8h total (103.3h initial + 20.5h resit), 41.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 11 students x 3h = 33.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x full-time PhD student × 80h/FTE; 1x assessor (8h each) = 248.0h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 112.0h</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>Internationalisation and Visitors Coordinator: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Detlef Plump</t>
+          <t>Soumya Banerjee</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>1088.76</v>
+        <v>856.04</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>325.16</v>
+        <v>516.8399999999999</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>260.2</v>
+        <v>164.2</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>503.4</v>
+        <v>175</v>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>THE2 (20cr): Standard (2.5x): 6.7h/teacher @ 2.5x = 16.7h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 318 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 125.7h total (104.9h initial + 20.8h resit), 41.9h per teacher; THE3 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; First time delivery: 5 groups shared by 3 lecturers for 3 weeks;   - New/new-content lecturer: 5.0h/week @ 5x (one first session per week);   - Standard lecturers (2): 2.5h/week @ 2.5x each (one first session per week); Repeated sessions: 2 group(s) without first-session slots, repeated weekly at 1.5x;   - Total repeat rate: 3.0h/week (1.0h/group × 2 groups × 1.5x); Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 313 scripts + 62 resits (assuming 20% of students resit) x 0.330h = 123.8h total (103.3h initial + 20.5h resit), 41.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 21 students x 3h = 63.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>AURO (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 104 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.9h total (34.3h initial + 6.6h resit), 13.6h per teacher; ELLA (20cr): New lecturer (5x): 6.0h base @ 2.5x + content dev = 30h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 13.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x assessor (8h each) = 96.0h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>EC Officer (on-campus): 15% of 1642h = 246.3h; Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Steven Wright</t>
+          <t>Stefano Pirandola</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>854.41</v>
+        <v>1257.515</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>227.21</v>
+        <v>315.815</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>452.2</v>
+        <v>520.4000000000001</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>175</v>
+        <v>421.3</v>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>HIPC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; First time delivery: 3 groups shared by 2 lecturers for 11 weeks;   - Standard lecturers (2): 5.0h/week @ 2.5x each (one first session per week); Repeated sessions: 1 group(s) without first-session slots, repeated weekly at 1.5x;   - Total repeat rate: 3.0h/week (2.0h/group × 1 groups × 1.5x); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 62 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 24.4h total (20.5h initial + 4.0h resit), 12.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 14 students x 3h = 42.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>QUCO (20cr): Standard (2.5x): 8.5h/teacher @ 2.5x = 21.2h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 51 scripts + 10 resits (assuming 20% of students resit) x 0.330h = 20.1h total (16.8h initial + 3.3h resit), 10.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x full-time PhD student × 80h/FTE; 1x part-time PhD student × 48h/FTE = 288.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h; Grant Integrated Quantum Networks (IQN) Hub: 10% of 1642h = 164.2h</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>Chair of the Board of Examiners: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Progression Panel Chair: 15% of 1642h = 246.3h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
@@ -3115,37 +3115,37 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Yuchen Zhao</t>
+          <t>Steven Wright</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>813.65</v>
+        <v>854.41</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>376.35</v>
+        <v>227.21</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>180.2</v>
+        <v>452.2</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>257.1</v>
+        <v>175</v>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>NETS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; First time delivery: 2 groups shared by 2 lecturers for 5 weeks;   - Standard lecturers (2): 5.0h/week @ 2.5x each (one first session per week); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 103 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.6h total (34.0h initial + 6.6h resit), 20.3h per teacher; EHAC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; First time delivery: 2 groups shared by 2 lecturers for 11 weeks;   - Standard lecturers (2): 5.0h/week @ 2.5x each (one first session per week); Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 56 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.1h total (18.5h initial + 3.6h resit), 11.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>HIPC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 62 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 24.4h total (20.5h initial + 4.0h resit), 12.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 14 students x 3h = 42.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x assessor (8h each) = 16.0h</t>
+          <t>PhD supervision: 3x full-time PhD student × 80h/FTE; 1x part-time PhD student × 48h/FTE = 288.0h</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Chair of the Board of Examiners: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
@@ -3162,37 +3162,37 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Carlo Ottaviani</t>
+          <t>Steven Xiaotian Dai</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>940.2816666666668</v>
+        <v>1179.32</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>332.8816666666667</v>
+        <v>325.62</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>268.2</v>
+        <v>350.3</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>339.2</v>
+        <v>503.4</v>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>CTAP (20cr): Standard (2.5x): 5.7h/teacher @ 2.5x = 14.2h; First time delivery: 2 groups shared by 3 lecturers for 1 weeks;   - Standard lecturers (3): 7.5h/week @ 2.5x each (one first session per week); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 89 scripts + 17 resits (assuming 20% of students resit) x 0.330h = 35.0h total (29.4h initial + 5.6h resit), 11.7h per teacher; PRAD (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; First time delivery: 2 groups shared by 2 lecturers for 11 weeks;   - Standard lecturers (2): 5.0h/week @ 2.5x each (one first session per week); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 56 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.1h total (18.5h initial + 3.6h resit), 11.1h per teacher; Project setting (fixed): 6.0h; Pastoral: 26 students x 3h = 78.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>EMBS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 45 scripts + 9 resits (assuming 20% of students resit) x 0.330h = 17.8h total (14.9h initial + 3.0h resit), 8.9h per teacher; HIPC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 62 scripts + 12 resits (assuming 20% of students resit) x 0.330h = 24.4h total (20.5h initial + 4.0h resit), 12.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 15 students x 3h = 45.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x assessor (8h each) = 104.0h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h; Grant SCHEME: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Student Disability Representative: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
@@ -3209,84 +3209,84 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Simon Foster</t>
+          <t>Tommy Yuan</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>728.2966666666666</v>
+        <v>1409.58</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>277.0966666666666</v>
+        <v>706.1800000000001</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>276.2</v>
+        <v>364.2</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>THE1 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; First time delivery: 4 groups shared by 3 lecturers for 11 weeks;   - Standard lecturers (3): 2.5h/week @ 2.5x each (one first session per week); Repeated sessions: 1 group(s) without first-session slots, repeated weekly at 1.5x;   - Total repeat rate: 1.5h/week (1.0h/group × 1 groups × 1.5x); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (2.5h main + 2.5h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; THE3 (20cr): Standard (2.5x): 6.3h/teacher @ 2.5x = 15.8h; First time delivery: 5 groups shared by 3 lecturers for 3 weeks;   - New/new-content lecturer: 5.0h/week @ 5x (one first session per week);   - Standard lecturers (2): 2.5h/week @ 2.5x each (one first session per week); Repeated sessions: 2 group(s) without first-session slots, repeated weekly at 1.5x;   - Total repeat rate: 3.0h/week (1.0h/group × 2 groups × 1.5x); Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 313 scripts + 62 resits (assuming 20% of students resit) x 0.330h = 123.8h total (103.3h initial + 20.5h resit), 41.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 11 students x 3h = 33.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>ARIA (20cr): Existing lecturer + new content (5x): 45h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; ENG1 (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 315 scripts + 63 resits (assuming 20% of students resit) x 0.330h = 124.7h total (104.0h initial + 20.8h resit), 41.6h per teacher; FOAM (20cr): Existing lecturer + new content (5x): 45h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 112.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 200.0h</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>CSCSE SQA Partnership Leader: 0% of 1642h = 0.0h; Deputy CBoEs: 10% of 1642h = 164.2h; StAMP committee members: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Module had 0 students - marking not calculated; Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Claudio Guarnera</t>
+          <t>Vasileios Vasilakis</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>668.24</v>
+        <v>968.1950000000001</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>217.04</v>
+        <v>272.795</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>276.2</v>
+        <v>356.2</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>IMLO (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; First time delivery: 4 groups shared by 3 lecturers for 11 weeks;   - Standard lecturers (3): 5.0h/week @ 2.5x each (one first session per week); Repeated sessions: 1 group(s) without first-session slots, repeated weekly at 1.5x;   - Total repeat rate: 3.0h/week (2.0h/group × 1 groups × 1.5x); Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 304 scripts + 60 resits (assuming 20% of students resit) x 0.330h = 120.1h total (100.3h initial + 19.8h resit), 40.0h per teacher; Project setting (fixed): 6.0h; Pastoral: 10 students x 3h = 30.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
+          <t>NETS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 103 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.6h total (34.0h initial + 6.6h resit), 20.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 26 students x 3h = 78.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 112.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Deputy CBoEs: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
@@ -3296,49 +3296,49 @@
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>James Stovold</t>
+          <t>William Smith</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>1011.84</v>
+        <v>1321.76</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>590.54</v>
+        <v>347.41</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>164.2</v>
+        <v>676.2</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>257.1</v>
+        <v>298.15</v>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>DEEP (20cr): New lecturer (5x): 9.0h base @ 2.5x + content dev = 45h; First time delivery: 3 groups shared by 2 lecturers for 11 weeks;   - New/new-content lecturer: 10.0h/week @ 5x (one first session per week);   - Standard lecturer: 5.0h/week @ 2.5x (one first session per week); Repeated sessions: 1 group(s) without first-session slots, repeated weekly at 1.5x;   - Total repeat rate: 3.0h/week (2.0h/group × 1 groups × 1.5x); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 130 scripts + 26 resits (assuming 20% of students resit) x 0.330h = 51.5h total (42.9h initial + 8.6h resit), 25.7h per teacher; LLMA (20cr): New lecturer (5x): 9.0h base @ 2.5x + content dev = 45h; First time delivery: 1 groups shared by 2 lecturers for 11 weeks;   - New/new-content lecturer: 10.0h/week @ 5x (one first session per week);   - Standard lecturer: 5.0h/week @ 2.5x (one first session per week); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>DEEP (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 130 scripts + 26 resits (assuming 20% of students resit) x 0.330h = 51.5h total (42.9h initial + 8.6h resit), 25.7h per teacher; ROCS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 82 scripts + 16 resits (assuming 20% of students resit) x 0.330h = 32.3h total (27.1h initial + 5.3h resit), 16.2h per teacher; Project setting (fixed): 6.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 4x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 6x assessor (8h each) = 512.0h</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Director of Admissions: 5% of 1642h = 82.1h; Internally Distributed Funding panel reviewer: 2% of 1642h = 41.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated; Module had 0 students - marking not calculated</t>
+          <t>Module had 0 students - marking not calculated</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
@@ -3350,37 +3350,37 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Paul Cairns</t>
+          <t>Xinwei Fang</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>1608.945</v>
+        <v>925.8049999999999</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>257.145</v>
+        <v>424.505</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>1012.6</v>
+        <v>244.2</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>339.2</v>
+        <v>257.1</v>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>HCIN (20cr): Standard (2.5x): 6.0h/teacher @ 2.5x = 15.0h; First time delivery: 4 groups shared by 3 lecturers for 11 weeks;   - Standard lecturers (3): 5.0h/week @ 2.5x each (one first session per week); Repeated sessions: 1 group(s) without first-session slots, repeated weekly at 1.5x;   - Total repeat rate: 3.0h/week (2.0h/group × 1 groups × 1.5x); Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (5.0h main + 5.0h resit); 282 scripts + 56 resits (assuming 20% of students resit) x 0.330h = 111.5h total (93.1h initial + 18.5h resit), 37.2h per teacher; GODS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; First time delivery: 2 groups shared by 2 lecturers for 11 weeks;   - Standard lecturers (2): 5.0h/week @ 2.5x each (one first session per week); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 18 scripts + 3 resits (assuming 20% of students resit) x 0.330h = 6.9h total (5.9h initial + 1.0h resit), 3.5h per teacher; Project setting (fixed): 6.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 1 projects x UG (16h) = 16.0h</t>
+          <t>DATA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 296 scripts + 59 resits (assuming 20% of students resit) x 0.330h = 117.2h total (97.7h initial + 19.5h resit), 58.6h per teacher; GPIG (40cr): Standard (2.5x): 19.0h/teacher @ 2.5x = 47.5h; Assessment setting: 6 paper(s) set (3 assessment(s), manual): 15.0h each (11.2h main + 11.2h resit); 35 scripts + 7 resits (assuming 20% of students resit) x 0.330h = 13.9h total (11.6h initial + 2.3h resit), 6.9h per teacher; Project setting (fixed): 6.0h; Pastoral: 9 students x 3h = 27.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 4x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 7x assessor (8h each) = 520.0h; Grant BiB Centre for Social Change: 0% of 1642h = 0.0h; Grant IGGI: 20% of 1642h = 328.4h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE = 80.0h</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>Other PLs: 5% of 1642h = 82.1h; REF Lead: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
@@ -3397,84 +3397,84 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Frank Soboczenski</t>
+          <t>Yan Jia</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>2157.82</v>
+        <v>952.3700000000001</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>106.3</v>
+        <v>138.67</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>1794.42</v>
+        <v>638.7</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>257.1</v>
+        <v>175</v>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>LLMA (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; First time delivery: 1 groups shared by 2 lecturers for 11 weeks;   - New/new-content lecturer: 10.0h/week @ 5x (one first session per week);   - Standard lecturer: 5.0h/week @ 2.5x (one first session per week); Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 100 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 39.6h total (33.0h initial + 6.6h resit), 19.8h per teacher; Also teaches: Artificial Intelligence (AI) (SAINTS - not included in workload)</t>
+          <t>ROCS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 82 scripts + 16 resits (assuming 20% of students resit) x 0.330h = 32.3h total (27.1h initial + 5.3h resit), 16.2h per teacher; Pastoral: 9 students x 3h = 27.0h; Also teaches: Designing Safe AI (Safe AI 2), Foundations of Safe AI (Safe AI 1) (SAINTS - not included in workload)</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 136.0h; Grant Large Language Models for lattice-theoretic reasoning of reactive programs: 11% of 1642h = 180.6h; Grant Alan Turing AI Fellowship: 80% of 1642h = 1313.6h</t>
+          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h; Grant Encoding Empathy: Solving the Healthcare Workforce Crisis Through the Safe Deployment of an AI-Driven Voice-Based Clinical Conversational Assistant for Long Term Monitoring: 10% of 1642h = 164.2h; Grant Addressing the healthcare workforce crisis with a multilingual, accessible phone-based conversational agent for cataract surgery follow up.: 10% of 1642h = 164.2h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>Module had 0 students - marking not calculated</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Iain Bate</t>
+          <t>Yuchen Zhao</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>2435.6</v>
+        <v>813.65</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>30</v>
+        <v>376.35</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>588.6</v>
+        <v>180.2</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>1817</v>
+        <v>257.1</v>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>Minimum administrative teaching load (from workload_parameters.yaml): 30h</t>
+          <t>EHAC (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 4 paper(s) set (2 assessment(s), manual): 15.0h each (7.5h main + 7.5h resit); 56 scripts + 11 resits (assuming 20% of students resit) x 0.330h = 22.1h total (18.5h initial + 3.6h resit), 11.1h per teacher; NETS (20cr): Standard (2.5x): 9.0h/teacher @ 2.5x = 22.5h; Assessment setting: 2 paper(s) set (1 assessment(s), manual): 15.0h each (3.8h main + 3.8h resit); 103 scripts + 20 resits (assuming 20% of students resit) x 0.330h = 40.6h total (34.0h initial + 6.6h resit), 20.3h per teacher; Project setting (fixed): 6.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x assessor (8h each) = 96.0h; Grant SCHEME: 20% of 1642h = 328.4h</t>
+          <t>PhD supervision: 2x assessor (8h each) = 16.0h</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>Head of Department: 100% of 1642h = 1642.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
@@ -3553,17 +3553,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Poonam Yadav</t>
+          <t>Adrian Bors</t>
         </is>
       </c>
       <c r="B2" s="7" t="n">
-        <v>254.12</v>
+        <v>347.3</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>1112.8</v>
+        <v>412.2</v>
       </c>
       <c r="D2" s="7" t="n">
-        <v>339.2</v>
+        <v>257.1</v>
       </c>
       <c r="E2" s="7">
         <f>SUM(B2:D2)</f>
@@ -3573,17 +3573,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Christopher Crispin-Bailey</t>
+          <t>Alena Denisova</t>
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>532.6533333333334</v>
+        <v>398.415</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>164.2</v>
+        <v>444.2</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>462.35</v>
+        <v>503.4</v>
       </c>
       <c r="E3" s="7">
         <f>SUM(B3:D3)</f>
@@ -3593,17 +3593,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pourya Shamsolmoali</t>
+          <t>Alvaro Miyazawa</t>
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>396.115</v>
+        <v>247.2166666666667</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>228.2</v>
+        <v>268.2</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>298.15</v>
+        <v>339.2</v>
       </c>
       <c r="E4" s="7">
         <f>SUM(B4:D4)</f>
@@ -3613,17 +3613,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tommy Yuan</t>
+          <t>Andrew Pomfret</t>
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>706.1800000000001</v>
+        <v>528.1433333333333</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>364.2</v>
+        <v>164.2</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>339.2</v>
+        <v>257.1</v>
       </c>
       <c r="E5" s="7">
         <f>SUM(B5:D5)</f>
@@ -3633,17 +3633,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Vasileios Vasilakis</t>
+          <t>Antonio Garcia-Dominguez</t>
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>272.795</v>
+        <v>279.12</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>356.2</v>
+        <v>644.6000000000001</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="E6" s="7">
         <f>SUM(B6:D6)</f>
@@ -3653,17 +3653,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Felix Ulrich-Oltean</t>
+          <t>Carlo Ottaviani</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>93.43000000000001</v>
+        <v>332.8816666666667</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>212.2</v>
+        <v>268.2</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="E7" s="7">
         <f>SUM(B7:D7)</f>
@@ -3673,17 +3673,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kostas Barmpis</t>
+          <t>Christopher Crispin-Bailey</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>402.5</v>
+        <v>532.6533333333334</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>548.6</v>
+        <v>164.2</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>175</v>
+        <v>462.35</v>
       </c>
       <c r="E8" s="7">
         <f>SUM(B8:D8)</f>
@@ -3693,17 +3693,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>James Walker</t>
+          <t>Claire Ingram</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>314.04</v>
+        <v>221.885</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>1000.8</v>
+        <v>164.2</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="E9" s="7">
         <f>SUM(B9:D9)</f>
@@ -3713,14 +3713,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Yan Jia</t>
+          <t>Claudio Guarnera</t>
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>138.67</v>
+        <v>217.04</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>638.7</v>
+        <v>276.2</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>175</v>
@@ -3733,17 +3733,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alvaro Miyazawa</t>
+          <t>Colin Paterson</t>
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>247.2166666666667</v>
+        <v>228.8</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>268.2</v>
+        <v>579.76</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="E11" s="7">
         <f>SUM(B11:D11)</f>
@@ -3753,14 +3753,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Rob Alexander</t>
+          <t>Da Li</t>
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>209.885</v>
+        <v>410.8</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>398.3</v>
+        <v>164.2</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>175</v>
@@ -3773,17 +3773,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ian Gray</t>
+          <t>Dawn H Wood</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>95.41</v>
+        <v>439.6833333333333</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>348.2</v>
+        <v>164.2</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>996</v>
+        <v>175</v>
       </c>
       <c r="E13" s="7">
         <f>SUM(B13:D13)</f>
@@ -3793,17 +3793,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Antonio Garcia-Dominguez</t>
+          <t>Detlef Plump</t>
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>279.12</v>
+        <v>325.16</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>644.6000000000001</v>
+        <v>260.2</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>175</v>
+        <v>503.4</v>
       </c>
       <c r="E14" s="7">
         <f>SUM(B14:D14)</f>
@@ -3813,17 +3813,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Dimitris Kolovos</t>
+          <t>Dimitar Kazakov</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>83.92</v>
+        <v>299.3</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>1114.9</v>
+        <v>620.2</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="E15" s="7">
         <f>SUM(B15:D15)</f>
@@ -3833,17 +3833,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Jacob Rigby</t>
+          <t>Dimitris Kolovos</t>
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>397.78</v>
+        <v>83.92</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>246.3</v>
+        <v>1114.9</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="E16" s="7">
         <f>SUM(B16:D16)</f>
@@ -3853,17 +3853,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Peter Nightingale</t>
+          <t>Fang Yan</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>601.03</v>
+        <v>324.8133333333333</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>300.2</v>
+        <v>164.2</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="E17" s="7">
         <f>SUM(B17:D17)</f>
@@ -3873,17 +3873,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Mike Freeman</t>
+          <t>Felix Ulrich-Oltean</t>
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>549.1433333333333</v>
+        <v>93.43000000000001</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>164.2</v>
+        <v>212.2</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>257.1</v>
+        <v>175</v>
       </c>
       <c r="E18" s="7">
         <f>SUM(B18:D18)</f>
@@ -3893,17 +3893,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alena Denisova</t>
+          <t>Frank Soboczenski</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>398.415</v>
+        <v>106.3</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>444.2</v>
+        <v>1794.42</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>503.4</v>
+        <v>257.1</v>
       </c>
       <c r="E19" s="7">
         <f>SUM(B19:D19)</f>
@@ -3913,17 +3913,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Robbert Jongeling</t>
+          <t>Iain Bate</t>
         </is>
       </c>
       <c r="B20" s="7" t="n">
-        <v>415.28</v>
+        <v>30</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>164.2</v>
+        <v>588.6</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>175</v>
+        <v>1817</v>
       </c>
       <c r="E20" s="7">
         <f>SUM(B20:D20)</f>
@@ -3933,17 +3933,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Joe Cutting</t>
+          <t>Ian Gray</t>
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>361.035</v>
+        <v>95.41</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>228.2</v>
+        <v>348.2</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>175</v>
+        <v>996</v>
       </c>
       <c r="E21" s="7">
         <f>SUM(B21:D21)</f>
@@ -3953,17 +3953,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Roberto Metere</t>
+          <t>Jacob Rigby</t>
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>436.2416666666667</v>
+        <v>397.78</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>268.2</v>
+        <v>246.3</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="E22" s="7">
         <f>SUM(B22:D22)</f>
@@ -3973,17 +3973,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Jo Iacovides</t>
+          <t>James Stovold</t>
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>350.355</v>
+        <v>590.54</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>348.2</v>
+        <v>164.2</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>339.2</v>
+        <v>257.1</v>
       </c>
       <c r="E23" s="7">
         <f>SUM(B23:D23)</f>
@@ -3993,14 +3993,14 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sam Braunstein</t>
+          <t>James Walker</t>
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>317.3916666666667</v>
+        <v>314.04</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>164.2</v>
+        <v>1000.8</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>175</v>
@@ -4013,17 +4013,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Steven Xiaotian Dai</t>
+          <t>Jen Beeston</t>
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>325.62</v>
+        <v>369.8</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>350.3</v>
+        <v>332.2</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>503.4</v>
+        <v>175</v>
       </c>
       <c r="E25" s="7">
         <f>SUM(B25:D25)</f>
@@ -4033,17 +4033,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Stefano Pirandola</t>
+          <t>Jo Iacovides</t>
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>315.815</v>
+        <v>350.355</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>520.4000000000001</v>
+        <v>348.2</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>421.3</v>
+        <v>339.2</v>
       </c>
       <c r="E26" s="7">
         <f>SUM(B26:D26)</f>
@@ -4053,17 +4053,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>William Smith</t>
+          <t>Joe Cutting</t>
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>347.41</v>
+        <v>361.035</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>676.2</v>
+        <v>228.2</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>298.15</v>
+        <v>175</v>
       </c>
       <c r="E27" s="7">
         <f>SUM(B27:D27)</f>
@@ -4073,17 +4073,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Dimitar Kazakov</t>
+          <t>Katrina Attwood</t>
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>299.3</v>
+        <v>444.56</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>620.2</v>
+        <v>212.2</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>175</v>
+        <v>503.4</v>
       </c>
       <c r="E28" s="7">
         <f>SUM(B28:D28)</f>
@@ -4113,14 +4113,14 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Dawn H Wood</t>
+          <t>Kostas Barmpis</t>
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>439.6833333333333</v>
+        <v>402.5</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>164.2</v>
+        <v>548.6</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>175</v>
@@ -4133,17 +4133,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Pengcheng Liu</t>
+          <t>Mike Freeman</t>
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>229.3</v>
+        <v>549.1433333333333</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>996.5800000000002</v>
+        <v>164.2</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="E31" s="7">
         <f>SUM(B31:D31)</f>
@@ -4153,17 +4153,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Radu Calinescu</t>
+          <t>Mike O'Dea</t>
         </is>
       </c>
       <c r="B32" s="7" t="n">
-        <v>150.43</v>
+        <v>198.575</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>918.7</v>
+        <v>164.2</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="E32" s="7">
         <f>SUM(B32:D32)</f>
@@ -4173,17 +4173,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Claire Ingram</t>
+          <t>Nick Pears</t>
         </is>
       </c>
       <c r="B33" s="7" t="n">
-        <v>221.885</v>
+        <v>213.0133333333333</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>164.2</v>
+        <v>428.2</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>257.1</v>
+        <v>831.8000000000001</v>
       </c>
       <c r="E33" s="7">
         <f>SUM(B33:D33)</f>
@@ -4193,17 +4193,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Da Li</t>
+          <t>Paul Cairns</t>
         </is>
       </c>
       <c r="B34" s="7" t="n">
-        <v>410.8</v>
+        <v>257.145</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>164.2</v>
+        <v>1012.6</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="E34" s="7">
         <f>SUM(B34:D34)</f>
@@ -4213,14 +4213,14 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Siamak Shahandashti</t>
+          <t>Pedro Ribeiro</t>
         </is>
       </c>
       <c r="B35" s="7" t="n">
-        <v>300.34</v>
+        <v>345.93</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>478.3</v>
+        <v>644.6</v>
       </c>
       <c r="D35" s="7" t="n">
         <v>339.2</v>
@@ -4233,14 +4233,14 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Fang Yan</t>
+          <t>Pengcheng Liu</t>
         </is>
       </c>
       <c r="B36" s="7" t="n">
-        <v>324.8133333333333</v>
+        <v>229.3</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>164.2</v>
+        <v>996.5800000000002</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>175</v>
@@ -4253,17 +4253,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Mike O'Dea</t>
+          <t>Peter Nightingale</t>
         </is>
       </c>
       <c r="B37" s="7" t="n">
-        <v>198.575</v>
+        <v>601.03</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>164.2</v>
+        <v>300.2</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>257.1</v>
+        <v>339.2</v>
       </c>
       <c r="E37" s="7">
         <f>SUM(B37:D37)</f>
@@ -4273,17 +4273,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Colin Paterson</t>
+          <t>Poonam Yadav</t>
         </is>
       </c>
       <c r="B38" s="7" t="n">
-        <v>228.8</v>
+        <v>254.12</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>579.76</v>
+        <v>1112.8</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="E38" s="7">
         <f>SUM(B38:D38)</f>
@@ -4293,17 +4293,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Xinwei Fang</t>
+          <t>Pourya Shamsolmoali</t>
         </is>
       </c>
       <c r="B39" s="7" t="n">
-        <v>424.505</v>
+        <v>396.115</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>244.2</v>
+        <v>228.2</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>257.1</v>
+        <v>298.15</v>
       </c>
       <c r="E39" s="7">
         <f>SUM(B39:D39)</f>
@@ -4313,17 +4313,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Pedro Ribeiro</t>
+          <t>Radu Calinescu</t>
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>345.93</v>
+        <v>150.43</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>644.6</v>
+        <v>918.7</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="E40" s="7">
         <f>SUM(B40:D40)</f>
@@ -4333,17 +4333,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Katrina Attwood</t>
+          <t>Rob Alexander</t>
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>444.56</v>
+        <v>209.885</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>212.2</v>
+        <v>398.3</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>503.4</v>
+        <v>175</v>
       </c>
       <c r="E41" s="7">
         <f>SUM(B41:D41)</f>
@@ -4353,11 +4353,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Soumya Banerjee</t>
+          <t>Robbert Jongeling</t>
         </is>
       </c>
       <c r="B42" s="7" t="n">
-        <v>516.8399999999999</v>
+        <v>415.28</v>
       </c>
       <c r="C42" s="7" t="n">
         <v>164.2</v>
@@ -4373,17 +4373,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Nick Pears</t>
+          <t>Roberto Metere</t>
         </is>
       </c>
       <c r="B43" s="7" t="n">
-        <v>213.0133333333333</v>
+        <v>436.2416666666667</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>428.2</v>
+        <v>268.2</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>831.8000000000001</v>
+        <v>175</v>
       </c>
       <c r="E43" s="7">
         <f>SUM(B43:D43)</f>
@@ -4393,14 +4393,14 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Jen Beeston</t>
+          <t>Sam Braunstein</t>
         </is>
       </c>
       <c r="B44" s="7" t="n">
-        <v>369.8</v>
+        <v>317.3916666666667</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>332.2</v>
+        <v>164.2</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>175</v>
@@ -4413,17 +4413,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Andrew Pomfret</t>
+          <t>Siamak Shahandashti</t>
         </is>
       </c>
       <c r="B45" s="7" t="n">
-        <v>528.1433333333333</v>
+        <v>300.34</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>164.2</v>
+        <v>478.3</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>257.1</v>
+        <v>339.2</v>
       </c>
       <c r="E45" s="7">
         <f>SUM(B45:D45)</f>
@@ -4433,17 +4433,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Adrian Bors</t>
+          <t>Simon Foster</t>
         </is>
       </c>
       <c r="B46" s="7" t="n">
-        <v>347.3</v>
+        <v>277.0966666666666</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>412.2</v>
+        <v>276.2</v>
       </c>
       <c r="D46" s="7" t="n">
-        <v>257.1</v>
+        <v>175</v>
       </c>
       <c r="E46" s="7">
         <f>SUM(B46:D46)</f>
@@ -4453,17 +4453,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Detlef Plump</t>
+          <t>Soumya Banerjee</t>
         </is>
       </c>
       <c r="B47" s="7" t="n">
-        <v>325.16</v>
+        <v>516.8399999999999</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>260.2</v>
+        <v>164.2</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>503.4</v>
+        <v>175</v>
       </c>
       <c r="E47" s="7">
         <f>SUM(B47:D47)</f>
@@ -4473,17 +4473,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Steven Wright</t>
+          <t>Stefano Pirandola</t>
         </is>
       </c>
       <c r="B48" s="7" t="n">
-        <v>227.21</v>
+        <v>315.815</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>452.2</v>
+        <v>520.4000000000001</v>
       </c>
       <c r="D48" s="7" t="n">
-        <v>175</v>
+        <v>421.3</v>
       </c>
       <c r="E48" s="7">
         <f>SUM(B48:D48)</f>
@@ -4493,17 +4493,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Yuchen Zhao</t>
+          <t>Steven Wright</t>
         </is>
       </c>
       <c r="B49" s="7" t="n">
-        <v>376.35</v>
+        <v>227.21</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>180.2</v>
+        <v>452.2</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>257.1</v>
+        <v>175</v>
       </c>
       <c r="E49" s="7">
         <f>SUM(B49:D49)</f>
@@ -4513,17 +4513,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Carlo Ottaviani</t>
+          <t>Steven Xiaotian Dai</t>
         </is>
       </c>
       <c r="B50" s="7" t="n">
-        <v>332.8816666666667</v>
+        <v>325.62</v>
       </c>
       <c r="C50" s="7" t="n">
-        <v>268.2</v>
+        <v>350.3</v>
       </c>
       <c r="D50" s="7" t="n">
-        <v>339.2</v>
+        <v>503.4</v>
       </c>
       <c r="E50" s="7">
         <f>SUM(B50:D50)</f>
@@ -4533,17 +4533,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Simon Foster</t>
+          <t>Tommy Yuan</t>
         </is>
       </c>
       <c r="B51" s="7" t="n">
-        <v>277.0966666666666</v>
+        <v>706.1800000000001</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>276.2</v>
+        <v>364.2</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="E51" s="7">
         <f>SUM(B51:D51)</f>
@@ -4553,17 +4553,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Claudio Guarnera</t>
+          <t>Vasileios Vasilakis</t>
         </is>
       </c>
       <c r="B52" s="7" t="n">
-        <v>217.04</v>
+        <v>272.795</v>
       </c>
       <c r="C52" s="7" t="n">
-        <v>276.2</v>
+        <v>356.2</v>
       </c>
       <c r="D52" s="7" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="E52" s="7">
         <f>SUM(B52:D52)</f>
@@ -4573,17 +4573,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>James Stovold</t>
+          <t>William Smith</t>
         </is>
       </c>
       <c r="B53" s="7" t="n">
-        <v>590.54</v>
+        <v>347.41</v>
       </c>
       <c r="C53" s="7" t="n">
-        <v>164.2</v>
+        <v>676.2</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>257.1</v>
+        <v>298.15</v>
       </c>
       <c r="E53" s="7">
         <f>SUM(B53:D53)</f>
@@ -4593,17 +4593,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Paul Cairns</t>
+          <t>Xinwei Fang</t>
         </is>
       </c>
       <c r="B54" s="7" t="n">
-        <v>257.145</v>
+        <v>424.505</v>
       </c>
       <c r="C54" s="7" t="n">
-        <v>1012.6</v>
+        <v>244.2</v>
       </c>
       <c r="D54" s="7" t="n">
-        <v>339.2</v>
+        <v>257.1</v>
       </c>
       <c r="E54" s="7">
         <f>SUM(B54:D54)</f>
@@ -4613,17 +4613,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Frank Soboczenski</t>
+          <t>Yan Jia</t>
         </is>
       </c>
       <c r="B55" s="7" t="n">
-        <v>106.3</v>
+        <v>138.67</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>1794.42</v>
+        <v>638.7</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>257.1</v>
+        <v>175</v>
       </c>
       <c r="E55" s="7">
         <f>SUM(B55:D55)</f>
@@ -4633,17 +4633,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Iain Bate</t>
+          <t>Yuchen Zhao</t>
         </is>
       </c>
       <c r="B56" s="7" t="n">
-        <v>30</v>
+        <v>376.35</v>
       </c>
       <c r="C56" s="7" t="n">
-        <v>588.6</v>
+        <v>180.2</v>
       </c>
       <c r="D56" s="7" t="n">
-        <v>1817</v>
+        <v>257.1</v>
       </c>
       <c r="E56" s="7">
         <f>SUM(B56:D56)</f>
